--- a/data/trans_dic/IP31C_R_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31C_R_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 14,28</t>
+          <t>1,31; 7,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,36</t>
+          <t>4,83; 17,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,09</t>
+          <t>3,8; 9,79</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 11,37</t>
+          <t>11,4; 20,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 15,93</t>
+          <t>6,02; 13,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,76</t>
+          <t>9,8; 15,91</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,14</t>
+          <t>5,36; 13,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 12,44</t>
+          <t>3,51; 13,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,49</t>
+          <t>5,34; 11,28</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 16,35</t>
+          <t>7,96; 16,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 15,7</t>
+          <t>8,6; 17,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 13,75</t>
+          <t>9,35; 15,36</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 9,38</t>
+          <t>8,8; 13,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,84</t>
+          <t>7,49; 11,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,89; 9,62</t>
+          <t>8,71; 11,83</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,17 +884,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>15532</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4933; 16319</t>
+          <t>1601; 9483</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>930; 8673</t>
+          <t>5726; 20229</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7190; 20269</t>
+          <t>9161; 23611</t>
         </is>
       </c>
     </row>
@@ -957,17 +957,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>64</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14386</t>
+          <t>34682</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42896</t>
+          <t>51515</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8795; 21066</t>
+          <t>26210; 46382</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19940; 39211</t>
+          <t>10825; 24835</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32212; 55041</t>
+          <t>40146; 65178</t>
         </is>
       </c>
     </row>
@@ -1030,17 +1030,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>25178</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2460; 11524</t>
+          <t>8923; 22334</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9069; 22785</t>
+          <t>5415; 20178</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13612; 31483</t>
+          <t>17136; 36194</t>
         </is>
       </c>
     </row>
@@ -1103,17 +1103,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18484</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36728</t>
+          <t>40620</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12505; 26804</t>
+          <t>13226; 27897</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12259; 27842</t>
+          <t>14058; 29065</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27786; 46912</t>
+          <t>30833; 50635</t>
         </is>
       </c>
     </row>
@@ -1176,17 +1176,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>167</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>48040</t>
+          <t>73317</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113304</t>
+          <t>132844</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36228; 61083</t>
+          <t>60289; 90234</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52179; 80544</t>
+          <t>46171; 73643</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96021; 134031</t>
+          <t>113299; 153988</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31C_R_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31C_R_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que realizan algún voluntariado (tasa de respuesta: 99,62%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,31; 7,74</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4,83; 17,06</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3,8; 9,79</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>15,09%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>9,36%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>11,4; 20,17</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6,02; 13,81</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9,8; 15,91</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>5,36; 13,41</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3,51; 13,07</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5,34; 11,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>7,96; 16,79</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8,6; 17,78</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9,35; 15,36</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>8,8; 13,17</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7,49; 11,95</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8,71; 11,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.03608478124271106</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.09369432421815028</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.06442592238315123</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4420</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11112</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15532</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.01307225165176935</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.04827698225425091</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.03800111902524429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1601; 9483</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5726; 20229</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9161; 23611</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.07742641039659585</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1705669984381361</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.09793919097041788</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1508533342407388</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.0936108119773848</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1257314568310642</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>34682</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>16832</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>51515</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.114003271287103</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.06019993124170866</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.09798364190580625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>26210; 46382</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>10825; 24835</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>40146; 65178</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.2017413824067314</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1381149571206951</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1590797624005302</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.08686940356247083</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.06938668344458629</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.0784584867150193</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>14466</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10713</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25178</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.0535861987762046</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.03507367352843865</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.05339876570695645</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>8923; 22334</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5415; 20178</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>17136; 36194</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1341230856522849</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1306973384569463</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1127860319620061</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1188522660314725</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1276415746733733</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1232115538417797</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>19749</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>20871</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>40620</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.07959309649982325</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.08597306664666594</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.09352598962152545</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>13226; 27897</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>14058; 29065</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>30833; 50635</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1678870078679056</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.177754859761652</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1535907185145738</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1070202744247137</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.09658715430753964</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1020793328945715</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>73317</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>59528</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>132844</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.08800393469622064</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.07491494069715941</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.08706008836467097</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>60289; 90234</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>46171; 73643</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>113299; 153988</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1317150284086639</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.1194896195260067</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.118326203526282</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que realizan algún voluntariado (tasa de respuesta: 99,62%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4420</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>11112</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>15532</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1601</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>5726</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>9161</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>9483</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>20229</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>23611</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>34682</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>16832</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>51515</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>26210</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>10825</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>40146</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>46382</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>24835</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>65178</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>14466</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>10713</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>25178</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>8923</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>5415</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>17136</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>22334</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>20178</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>36194</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>19749</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>20871</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>40620</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>13226</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>14058</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>30833</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>27897</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>29065</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>50635</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>73317</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>59528</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>132844</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>60289</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>113299</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>90234</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>73643</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>153988</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>